--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_22.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_22.xlsx
@@ -471,11 +471,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56272</v>
+        <v>41710</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nathan Dias</t>
+          <t>Amanda da Conceição</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -485,26 +485,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45089</v>
+        <v>45081</v>
       </c>
       <c r="G2" t="n">
-        <v>10988.38</v>
+        <v>3565.94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14672</v>
+        <v>18619</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leonardo Pereira</t>
+          <t>Luana Cardoso</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,31 +514,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45102</v>
+        <v>45086</v>
       </c>
       <c r="G3" t="n">
-        <v>7202.1</v>
+        <v>11361.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>42295</v>
+        <v>77456</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vitor Mendes</t>
+          <t>Bruno da Paz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,216 +547,216 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45080</v>
+        <v>45081</v>
       </c>
       <c r="G4" t="n">
-        <v>4312.12</v>
+        <v>10187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77845</v>
+        <v>74366</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dra. Emanuella Porto</t>
+          <t>Antônio Cardoso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45105</v>
+        <v>45091</v>
       </c>
       <c r="G5" t="n">
-        <v>7321.46</v>
+        <v>8959.700000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89945</v>
+        <v>29483</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sra. Júlia Almeida</t>
+          <t>Marcela Peixoto</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45094</v>
+        <v>45093</v>
       </c>
       <c r="G6" t="n">
-        <v>3723.13</v>
+        <v>5668.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>580</v>
+        <v>11275</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arthur Moreira</t>
+          <t>Dr. Matheus Cardoso</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45080</v>
+        <v>45088</v>
       </c>
       <c r="G7" t="n">
-        <v>9249.32</v>
+        <v>7391.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5785</v>
+        <v>61877</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vitor Gabriel da Cunha</t>
+          <t>Sra. Joana Pereira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45087</v>
+        <v>45089</v>
       </c>
       <c r="G8" t="n">
-        <v>10990.16</v>
+        <v>9856.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57904</v>
+        <v>21766</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gabrielly Pires</t>
+          <t>João Vitor Peixoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45082</v>
+        <v>45097</v>
       </c>
       <c r="G9" t="n">
-        <v>10313.7</v>
+        <v>9379.889999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2873</v>
+        <v>630</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thales Lopes</t>
+          <t>Vitória da Rosa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45083</v>
+        <v>45085</v>
       </c>
       <c r="G10" t="n">
-        <v>11484.13</v>
+        <v>3213.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1100</v>
+        <v>84484</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luiz Otávio da Cunha</t>
+          <t>Srta. Brenda Souza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45085</v>
+        <v>45102</v>
       </c>
       <c r="G11" t="n">
-        <v>6114.83</v>
+        <v>2991.21</v>
       </c>
     </row>
   </sheetData>
